--- a/verificables revisión sistemática/S14_extraccion_adjudicada.xlsx
+++ b/verificables revisión sistemática/S14_extraccion_adjudicada.xlsx
@@ -3737,7 +3737,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>fago en monoterapia</t>
+          <t>fago + antibiótico</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>fago en monoterapia</t>
+          <t>fago + antibiótico</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -9680,7 +9680,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>fago en monoterapia</t>
+          <t>fago + antibiótico</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -12246,7 +12246,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>fago en monoterapia</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -15147,7 +15147,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>fago en monoterapia</t>
+          <t>fago + antibiótico</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">

--- a/verificables revisión sistemática/S14_extraccion_adjudicada.xlsx
+++ b/verificables revisión sistemática/S14_extraccion_adjudicada.xlsx
@@ -829,7 +829,7 @@
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-01</t>
+          <t>Generado el 2026-09-02</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S14_extraccion_adjudicada.xlsx
+++ b/verificables revisión sistemática/S14_extraccion_adjudicada.xlsx
@@ -829,7 +829,7 @@
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-02</t>
+          <t>Generado el 2026-09-14</t>
         </is>
       </c>
     </row>
@@ -6927,7 +6927,11 @@
           <t>tópica o local</t>
         </is>
       </c>
-      <c r="W52" t="inlineStr"/>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>reporte de caso único</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -12313,12 +12317,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Anticuerpos pueden persistir &gt;1 año; no correlaciona con fallo</t>
+          <t>Categorías A-G de Międzybrodzki, definidas literalmente en el artículo. A-C son respuestas positivas (A: erradicación del patógeno y/o recuperación; B: buen resultado clínico; C: mejoría clínica). D-G son respuestas inadecuadas.</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -12333,7 +12337,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>completa</t>
+          <t>parcial</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -12373,12 +12377,12 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>mixto, con subgrupo separable</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
@@ -12403,12 +12407,12 @@
       </c>
       <c r="V99" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>tópica o local</t>
         </is>
       </c>
       <c r="W99" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>serie de casos</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S14_extraccion_adjudicada.xlsx
+++ b/verificables revisión sistemática/S14_extraccion_adjudicada.xlsx
@@ -1026,7 +1026,11 @@
           <t>Informe del caso</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>completa</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>Francia</t>
@@ -3897,7 +3901,11 @@
           <t>intravenosa</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr"/>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>otra</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -5899,7 +5907,11 @@
           <t>A</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
           <t>SIN DEFINICION OPERATIVA</t>
@@ -6881,7 +6893,11 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr">
         <is>
           <t>fago + antibiótico</t>
@@ -7746,7 +7762,11 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="W59" t="inlineStr"/>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>serie de casos</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -8678,7 +8698,11 @@
           <t>tópica o local</t>
         </is>
       </c>
-      <c r="W67" t="inlineStr"/>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>otra</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -10780,7 +10804,11 @@
           <t>intravenosa</t>
         </is>
       </c>
-      <c r="W85" t="inlineStr"/>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>serie de casos</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -11946,7 +11974,11 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="W95" t="inlineStr"/>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>otra</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -13346,7 +13378,11 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="W107" t="inlineStr"/>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>otra</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -14157,7 +14193,11 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="W114" t="inlineStr"/>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>ensayo aleatorizado</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -14504,7 +14544,11 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="W117" t="inlineStr"/>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>cohorte prospectiva</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -14542,7 +14586,11 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr"/>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>parcial</t>
+        </is>
+      </c>
       <c r="I118" t="inlineStr">
         <is>
           <t>INDIA</t>
@@ -16364,7 +16412,11 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="W133" t="inlineStr"/>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>otra</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:W133"/>

--- a/verificables revisión sistemática/S14_extraccion_adjudicada.xlsx
+++ b/verificables revisión sistemática/S14_extraccion_adjudicada.xlsx
@@ -829,7 +829,7 @@
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-14</t>
+          <t>Generado el 2026-09-15</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S14_extraccion_adjudicada.xlsx
+++ b/verificables revisión sistemática/S14_extraccion_adjudicada.xlsx
@@ -829,7 +829,7 @@
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-15</t>
+          <t>Generado el 2026-09-16</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S14_extraccion_adjudicada.xlsx
+++ b/verificables revisión sistemática/S14_extraccion_adjudicada.xlsx
@@ -829,7 +829,7 @@
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-16</t>
+          <t>Generado el 2026-09-22</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S14_extraccion_adjudicada.xlsx
+++ b/verificables revisión sistemática/S14_extraccion_adjudicada.xlsx
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>"Significant reductions of P. aeruginosa colony forming units (CFU) in sputum occurred in the treatment arm compared to placebo, on days 4 (1.9 log10 CFU per gram of sputum difference between groups, p =0.035) and 15 (2.7 log10 CFU per gram of sputum difference between groups, p = 0.029)... Taken together, these data demonstrate the favorable safety profile, feasibility of lower respiratory tract delivery, and preliminary indications of antimicrobial efficacy of the BX004-A phage cocktail."</t>
+          <t>Recovery which was defined as no clinical signs of infection detected by physical examinations or PET/MRI imaging and negative microbiological cultures from site of infection; Remission defined as no clinical signs of infection or no imaging findings that suggest an active infection is present, however bacterial cultures were not obtained during the entire follow-up period.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>"Significant reductions of P. aeruginosa colony forming units (CFU) in sputum occurred in the treatment arm compared to placebo, on days 4 (1.9 log10 CFU per gram of sputum difference between groups, p =0.035) and 15 (2.7 log10 CFU per gram of sputum difference between groups, p = 0.029)... Taken together, these data demonstrate the favorable safety profile, feasibility of lower respiratory tract delivery, and preliminary indications of antimicrobial efficacy of the BX004-A phage cocktail."</t>
+          <t>Recovery which was defined as no clinical signs of infection detected by physical examinations or PET/MRI imaging and negative microbiological cultures from site of infection; Remission defined as no clinical signs of infection or no imaging findings that suggest an active infection is present, however bacterial cultures were not obtained during the entire follow-up period.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>"Significant reductions of P. aeruginosa colony forming units (CFU) in sputum occurred in the treatment arm compared to placebo, on days 4 (1.9 log10 CFU per gram of sputum difference between groups, p =0.035) and 15 (2.7 log10 CFU per gram of sputum difference between groups, p = 0.029)... Taken together, these data demonstrate the favorable safety profile, feasibility of lower respiratory tract delivery, and preliminary indications of antimicrobial efficacy of the BX004-A phage cocktail."</t>
+          <t>Recovery which was defined as no clinical signs of infection detected by physical examinations or PET/MRI imaging and negative microbiological cultures from site of infection; Remission defined as no clinical signs of infection or no imaging findings that suggest an active infection is present, however bacterial cultures were not obtained during the entire follow-up period.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>"Significant reductions of P. aeruginosa colony forming units (CFU) in sputum occurred in the treatment arm compared to placebo, on days 4 (1.9 log10 CFU per gram of sputum difference between groups, p =0.035) and 15 (2.7 log10 CFU per gram of sputum difference between groups, p = 0.029)... Taken together, these data demonstrate the favorable safety profile, feasibility of lower respiratory tract delivery, and preliminary indications of antimicrobial efficacy of the BX004-A phage cocktail."</t>
+          <t>Recovery which was defined as no clinical signs of infection detected by physical examinations or PET/MRI imaging and negative microbiological cultures from site of infection; Remission defined as no clinical signs of infection or no imaging findings that suggest an active infection is present, however bacterial cultures were not obtained during the entire follow-up period.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>"Significant reductions of P. aeruginosa colony forming units (CFU) in sputum occurred in the treatment arm compared to placebo, on days 4 (1.9 log10 CFU per gram of sputum difference between groups, p =0.035) and 15 (2.7 log10 CFU per gram of sputum difference between groups, p = 0.029)... Taken together, these data demonstrate the favorable safety profile, feasibility of lower respiratory tract delivery, and preliminary indications of antimicrobial efficacy of the BX004-A phage cocktail."</t>
+          <t>Recovery which was defined as no clinical signs of infection detected by physical examinations or PET/MRI imaging and negative microbiological cultures from site of infection; Remission defined as no clinical signs of infection or no imaging findings that suggest an active infection is present, however bacterial cultures were not obtained during the entire follow-up period.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>13</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">

--- a/verificables revisión sistemática/S14_extraccion_adjudicada.xlsx
+++ b/verificables revisión sistemática/S14_extraccion_adjudicada.xlsx
@@ -829,7 +829,7 @@
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-22</t>
+          <t>Generado el 2026-09-23</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S14_extraccion_adjudicada.xlsx
+++ b/verificables revisión sistemática/S14_extraccion_adjudicada.xlsx
@@ -829,7 +829,7 @@
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-23</t>
+          <t>Generado el 2026-10-03</t>
         </is>
       </c>
     </row>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>declarado por el autor</t>
+          <t>verificado de forma independiente</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>declarado por el autor</t>
+          <t>verificado de forma independiente</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>declarado por el autor</t>
+          <t>verificado de forma independiente</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>declarado por el autor</t>
+          <t>verificado de forma independiente</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>PDR</t>
+          <t>XDR</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>declarado por el autor</t>
+          <t>verificado de forma independiente</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3771,7 +3771,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>declarado por el autor</t>
+          <t>verificado de forma independiente</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no derivable</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>declarado por el autor</t>
+          <t>verificado de forma independiente</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -5807,7 +5807,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -5989,12 +5989,12 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>MDR</t>
+          <t>XDR</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>declarado por el autor</t>
+          <t>verificado de forma independiente</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -6111,7 +6111,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>declarado por el autor</t>
+          <t>verificado de forma independiente</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -6275,7 +6275,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6340,7 +6340,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>no clasificable</t>
+          <t>XDR</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
@@ -6392,7 +6392,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>MDR</t>
+          <t>XDR</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>declarado por el autor</t>
+          <t>verificado de forma independiente</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>MDR</t>
+          <t>no clasificable</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>no clasificable</t>
+          <t>por debajo de MDR</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
@@ -7510,7 +7510,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>no clasificable</t>
+          <t>por debajo de MDR</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -7632,7 +7632,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>declarado por el autor</t>
+          <t>verificado de forma independiente</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -7913,7 +7913,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -7983,7 +7983,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>declarado por el autor</t>
+          <t>verificado de forma independiente</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -9738,7 +9738,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>declarado por el autor</t>
+          <t>verificado de forma independiente</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>no clasificable</t>
+          <t>por debajo de MDR</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>declarado por el autor</t>
+          <t>verificado de forma independiente</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>declarado por el autor</t>
+          <t>verificado de forma independiente</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no derivable</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>declarado por el autor</t>
+          <t>verificado de forma independiente</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -11072,7 +11072,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -11137,7 +11137,7 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>no clasificable</t>
+          <t>XDR</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
@@ -11254,7 +11254,7 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>MDR</t>
+          <t>por debajo de MDR</t>
         </is>
       </c>
       <c r="T89" t="inlineStr">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -12658,12 +12658,12 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>MDR</t>
+          <t>XDR</t>
         </is>
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>declarado por el autor</t>
+          <t>verificado de forma independiente</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
@@ -14344,7 +14344,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -14414,7 +14414,7 @@
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>declarado por el autor</t>
+          <t>verificado de forma independiente</t>
         </is>
       </c>
       <c r="U116" t="inlineStr">

--- a/verificables revisión sistemática/S14_extraccion_adjudicada.xlsx
+++ b/verificables revisión sistemática/S14_extraccion_adjudicada.xlsx
@@ -829,7 +829,7 @@
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-03</t>
+          <t>Generado el 2026-10-06</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S14_extraccion_adjudicada.xlsx
+++ b/verificables revisión sistemática/S14_extraccion_adjudicada.xlsx
@@ -829,7 +829,7 @@
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-06</t>
+          <t>Generado el 2026-10-07</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S14_extraccion_adjudicada.xlsx
+++ b/verificables revisión sistemática/S14_extraccion_adjudicada.xlsx
@@ -829,7 +829,7 @@
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-07</t>
+          <t>Generado el 2026-10-08</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S14_extraccion_adjudicada.xlsx
+++ b/verificables revisión sistemática/S14_extraccion_adjudicada.xlsx
@@ -829,7 +829,7 @@
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-08</t>
+          <t>Generado el 2026-10-12</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S14_extraccion_adjudicada.xlsx
+++ b/verificables revisión sistemática/S14_extraccion_adjudicada.xlsx
@@ -829,7 +829,7 @@
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-12</t>
+          <t>Generado el 2026-10-14</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S14_extraccion_adjudicada.xlsx
+++ b/verificables revisión sistemática/S14_extraccion_adjudicada.xlsx
@@ -829,7 +829,7 @@
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-14</t>
+          <t>Generado el 2026-10-15</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S14_extraccion_adjudicada.xlsx
+++ b/verificables revisión sistemática/S14_extraccion_adjudicada.xlsx
@@ -829,7 +829,7 @@
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-15</t>
+          <t>Generado el 2026-10-19</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S14_extraccion_adjudicada.xlsx
+++ b/verificables revisión sistemática/S14_extraccion_adjudicada.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,6 +41,10 @@
       <b val="1"/>
       <color rgb="001F4E79"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -89,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -100,11 +104,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -472,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -499,7 +506,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Anexo del material suplementario.</t>
+          <t>La extracción definitiva: un valor por casilla, brazo a brazo, tras la adjudicación de los desacuerdos entre las dos extracciones, cuya independencia no está acreditada (S11). De dónde sale cada valor (acuerdo, adjudicada por los dos o por uno, corregida contra el texto, una sola lectura o abierta) está en S15, que tiene la misma forma. De sus 132 filas, 59 son brazos de estudios que salieron después del cribado (S16); la sección y las tablas que se citan abajo cuentan solo los 73 brazos de los estudios que siguen en el corpus.</t>
         </is>
       </c>
     </row>
@@ -514,320 +521,331 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr"/>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Sostiene la sección 3.5 (tabla 5) y el embudo de agregabilidad (sección 3.6, tabla 6).</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Las secciones y tablas que se citan son las del informe extendido (manuscrito maestro). En el manuscrito preparado para la revista las secciones no van numeradas; allí la tabla 5 (desenlaces) es la Tabla 4.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Cuántas filas</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>132 filas de datos</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
-    </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Qué significa cada columna</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Estudio</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>columna interna: study_id</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Brazo</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>columna interna: arm_id</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>adverse_event_n</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Eventos adversos (nº)</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>columna interna: adverse_event_n</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>clinical_success_definition</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>¿Cómo define el AUTOR el éxito clínico?</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>columna interna: clinical_success_definition</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>clinical_success_n</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Éxito clínico (nº pacientes)</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>columna interna: clinical_success_n</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>¿Cumple criterio DTR?</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>columna interna: dtr_status</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>extraction_citation</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>¿Dónde viste estos datos?</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>columna interna: extraction_citation</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>Estado de la extracción</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>columna interna: extraction_status</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>geographic_source</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>País del estudio</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>columna interna: geographic_source</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>incomplete_reason</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Si algo quedó incompleto, ¿por qué?</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>columna interna: incomplete_reason</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>journal_tier</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Nivel de la revista</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>columna interna: journal_tier</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>los_days</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Estancia hospitalaria (días)</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>columna interna: los_days</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>microbio_eradication_n</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Erradicación microbiológica (nº)</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>columna interna: microbio_eradication_n</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>¿Fago solo o con antibiótico?</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>columna interna: modality</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>mortality_n</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Fallecidos (nº)</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>columna interna: mortality_n</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>Pacientes en el brazo</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>columna interna: n_arm</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>¿Solo P. aeruginosa o mixto?</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>columna interna: pathogen_scope</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>publication_year</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Año de publicación</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>columna interna: publication_year</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>Clase de resistencia</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>columna interna: resistance_class</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>De dónde sale la clase</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>columna interna: resistance_class_source</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>resistance_emergence_n</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Aparición de resistencia al fago (nº)</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>columna interna: resistance_emergence_n</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>Vía de administración</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>columna interna: route</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>Diseño del estudio</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>columna interna: study_design</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="6" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>El CSV con los nombres internos acompaña a este fichero: es la copia reproducible.</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="7" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>Generado el 2026-10-19</t>
         </is>
@@ -873,117 +891,117 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Estudio</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>Brazo</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
-        <is>
-          <t>adverse_event_n</t>
-        </is>
-      </c>
-      <c r="D1" s="8" t="inlineStr">
-        <is>
-          <t>clinical_success_definition</t>
-        </is>
-      </c>
-      <c r="E1" s="8" t="inlineStr">
-        <is>
-          <t>clinical_success_n</t>
-        </is>
-      </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>Eventos adversos (nº)</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>¿Cómo define el AUTOR el éxito clínico?</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>Éxito clínico (nº pacientes)</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>¿Cumple criterio DTR?</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
-        <is>
-          <t>extraction_citation</t>
-        </is>
-      </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>¿Dónde viste estos datos?</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>Estado de la extracción</t>
         </is>
       </c>
-      <c r="I1" s="8" t="inlineStr">
-        <is>
-          <t>geographic_source</t>
-        </is>
-      </c>
-      <c r="J1" s="8" t="inlineStr">
-        <is>
-          <t>incomplete_reason</t>
-        </is>
-      </c>
-      <c r="K1" s="8" t="inlineStr">
-        <is>
-          <t>journal_tier</t>
-        </is>
-      </c>
-      <c r="L1" s="8" t="inlineStr">
-        <is>
-          <t>los_days</t>
-        </is>
-      </c>
-      <c r="M1" s="8" t="inlineStr">
-        <is>
-          <t>microbio_eradication_n</t>
-        </is>
-      </c>
-      <c r="N1" s="8" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t>País del estudio</t>
+        </is>
+      </c>
+      <c r="J1" s="9" t="inlineStr">
+        <is>
+          <t>Si algo quedó incompleto, ¿por qué?</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="inlineStr">
+        <is>
+          <t>Nivel de la revista</t>
+        </is>
+      </c>
+      <c r="L1" s="9" t="inlineStr">
+        <is>
+          <t>Estancia hospitalaria (días)</t>
+        </is>
+      </c>
+      <c r="M1" s="9" t="inlineStr">
+        <is>
+          <t>Erradicación microbiológica (nº)</t>
+        </is>
+      </c>
+      <c r="N1" s="9" t="inlineStr">
         <is>
           <t>¿Fago solo o con antibiótico?</t>
         </is>
       </c>
-      <c r="O1" s="8" t="inlineStr">
-        <is>
-          <t>mortality_n</t>
-        </is>
-      </c>
-      <c r="P1" s="8" t="inlineStr">
+      <c r="O1" s="9" t="inlineStr">
+        <is>
+          <t>Fallecidos (nº)</t>
+        </is>
+      </c>
+      <c r="P1" s="9" t="inlineStr">
         <is>
           <t>Pacientes en el brazo</t>
         </is>
       </c>
-      <c r="Q1" s="8" t="inlineStr">
+      <c r="Q1" s="9" t="inlineStr">
         <is>
           <t>¿Solo P. aeruginosa o mixto?</t>
         </is>
       </c>
-      <c r="R1" s="8" t="inlineStr">
-        <is>
-          <t>publication_year</t>
-        </is>
-      </c>
-      <c r="S1" s="8" t="inlineStr">
+      <c r="R1" s="9" t="inlineStr">
+        <is>
+          <t>Año de publicación</t>
+        </is>
+      </c>
+      <c r="S1" s="9" t="inlineStr">
         <is>
           <t>Clase de resistencia</t>
         </is>
       </c>
-      <c r="T1" s="8" t="inlineStr">
+      <c r="T1" s="9" t="inlineStr">
         <is>
           <t>De dónde sale la clase</t>
         </is>
       </c>
-      <c r="U1" s="8" t="inlineStr">
-        <is>
-          <t>resistance_emergence_n</t>
-        </is>
-      </c>
-      <c r="V1" s="8" t="inlineStr">
+      <c r="U1" s="9" t="inlineStr">
+        <is>
+          <t>Aparición de resistencia al fago (nº)</t>
+        </is>
+      </c>
+      <c r="V1" s="9" t="inlineStr">
         <is>
           <t>Vía de administración</t>
         </is>
       </c>
-      <c r="W1" s="8" t="inlineStr">
+      <c r="W1" s="9" t="inlineStr">
         <is>
           <t>Diseño del estudio</t>
         </is>

--- a/verificables revisión sistemática/S14_extraccion_adjudicada.xlsx
+++ b/verificables revisión sistemática/S14_extraccion_adjudicada.xlsx
@@ -847,7 +847,7 @@
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-19</t>
+          <t>Generado el 2026-10-20</t>
         </is>
       </c>
     </row>
